--- a/artfynd/A 22071-2022 artfynd.xlsx
+++ b/artfynd/A 22071-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127125690</v>
       </c>
       <c r="B2" t="n">
-        <v>75014</v>
+        <v>75073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127123940</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127124504</v>
       </c>
       <c r="B5" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22071-2022 artfynd.xlsx
+++ b/artfynd/A 22071-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127125690</v>
       </c>
       <c r="B2" t="n">
-        <v>75073</v>
+        <v>75076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127123940</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127124504</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22071-2022 artfynd.xlsx
+++ b/artfynd/A 22071-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127125690</v>
       </c>
       <c r="B2" t="n">
-        <v>75076</v>
+        <v>75080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127125709</v>
       </c>
       <c r="B3" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127123940</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127124504</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127123766</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22071-2022 artfynd.xlsx
+++ b/artfynd/A 22071-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127125690</v>
       </c>
       <c r="B2" t="n">
-        <v>75080</v>
+        <v>75082</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127123940</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127124504</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127123766</v>
       </c>
       <c r="B6" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22071-2022 artfynd.xlsx
+++ b/artfynd/A 22071-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127125690</v>
       </c>
       <c r="B2" t="n">
-        <v>75082</v>
+        <v>75085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127123940</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127124504</v>
       </c>
       <c r="B5" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127123766</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22071-2022 artfynd.xlsx
+++ b/artfynd/A 22071-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127125690</v>
       </c>
       <c r="B2" t="n">
-        <v>75085</v>
+        <v>75091</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127123940</v>
       </c>
       <c r="B4" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127124504</v>
       </c>
       <c r="B5" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127123766</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22071-2022 artfynd.xlsx
+++ b/artfynd/A 22071-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127125690</v>
       </c>
       <c r="B2" t="n">
-        <v>75091</v>
+        <v>75073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127125709</v>
       </c>
       <c r="B3" t="n">
-        <v>8439</v>
+        <v>8436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127123940</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127124504</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127123766</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22071-2022 artfynd.xlsx
+++ b/artfynd/A 22071-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127125690</v>
       </c>
       <c r="B2" t="n">
-        <v>75073</v>
+        <v>75091</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127125709</v>
       </c>
       <c r="B3" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127123940</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127124504</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127123766</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22071-2022 artfynd.xlsx
+++ b/artfynd/A 22071-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>127125690</v>
       </c>
       <c r="B2" t="n">
-        <v>75091</v>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -772,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127125709</v>
+        <v>127123940</v>
       </c>
       <c r="B3" t="n">
-        <v>8439</v>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tomossfly, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726834</v>
+        <v>726968</v>
       </c>
       <c r="R3" t="n">
-        <v>6640927</v>
+        <v>6640748</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127123940</v>
+        <v>127124504</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726968</v>
+        <v>726949</v>
       </c>
       <c r="R4" t="n">
-        <v>6640748</v>
+        <v>6640794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,45 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127124504</v>
+        <v>127123766</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tomossfly, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>726949</v>
+        <v>726981</v>
       </c>
       <c r="R5" t="n">
-        <v>6640794</v>
+        <v>6640701</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,38 +1068,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127123766</v>
+        <v>127125709</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>8444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>726981</v>
+        <v>726834</v>
       </c>
       <c r="R6" t="n">
-        <v>6640701</v>
+        <v>6640927</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1167,107 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119136934</v>
+      </c>
+      <c r="B7" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skeppsmyra, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>726862</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6640663</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Björkö-Arholma</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karin Agstam-Norlin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karin Agstam-Norlin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22071-2022 artfynd.xlsx
+++ b/artfynd/A 22071-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127125690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127123940</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127124504</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127123766</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127125709</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,8 +1298,21 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119136934</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>